--- a/artfynd/A 58719-2021 artfynd.xlsx
+++ b/artfynd/A 58719-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58719-2021 artfynd.xlsx
+++ b/artfynd/A 58719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96801489</v>
+        <v>97330365</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555009.2303042959</v>
+        <v>555038</v>
       </c>
       <c r="R2" t="n">
-        <v>6698357.292026086</v>
+        <v>6698219</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,22 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,64 +780,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96801471</v>
+        <v>97330373</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555012.2283995657</v>
+        <v>554999</v>
       </c>
       <c r="R3" t="n">
-        <v>6698355.361516474</v>
+        <v>6698264</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,68 +888,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96800225</v>
+        <v>99589184</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555012.5133991292</v>
+        <v>555018</v>
       </c>
       <c r="R4" t="n">
-        <v>6698369.197604009</v>
+        <v>6698279</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,22 +975,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjolårsfru</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,76 +1010,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97120701</v>
+        <v>112044197</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555062.9191937479</v>
+        <v>555034</v>
       </c>
       <c r="R5" t="n">
-        <v>6698308.212907644</v>
+        <v>6698209</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,76 +1107,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97121317</v>
+        <v>112044198</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555001.2254161108</v>
+        <v>555034</v>
       </c>
       <c r="R6" t="n">
-        <v>6698363.098562525</v>
+        <v>6698210</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,22 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,76 +1204,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97120236</v>
+        <v>112044200</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555089.1163704504</v>
+        <v>555046</v>
       </c>
       <c r="R7" t="n">
-        <v>6698212.279465104</v>
+        <v>6698231</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,22 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,76 +1301,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97121323</v>
+        <v>112044165</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554995.4239049952</v>
+        <v>555063</v>
       </c>
       <c r="R8" t="n">
-        <v>6698354.118756627</v>
+        <v>6698317</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,22 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,27 +1398,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97120331</v>
+        <v>97121369</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,46 +1421,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555148.7360116865</v>
+        <v>554998</v>
       </c>
       <c r="R9" t="n">
-        <v>6698228.993575117</v>
+        <v>6698350</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1600,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,73 +1515,58 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97120882</v>
+        <v>97330695</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555020.5332726752</v>
+        <v>554976</v>
       </c>
       <c r="R10" t="n">
-        <v>6698362.4033461</v>
+        <v>6698330</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1718,22 +1593,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,73 +1623,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97121049</v>
+        <v>99589220</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555002.3345950861</v>
+        <v>555011</v>
       </c>
       <c r="R11" t="n">
-        <v>6698355.211506072</v>
+        <v>6698313</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1841,29 +1707,34 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning under betad gammal tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1871,73 +1742,69 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97121134</v>
+        <v>97120331</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555002.1848442798</v>
+        <v>555149</v>
       </c>
       <c r="R12" t="n">
-        <v>6698365.089073376</v>
+        <v>6698229</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1969,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,27 +1861,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97121063</v>
+        <v>96800107</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,12 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2057,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555012.6931339417</v>
+        <v>555001</v>
       </c>
       <c r="R13" t="n">
-        <v>6698357.34453325</v>
+        <v>6698393</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2087,22 +1944,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,72 +1974,63 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97121369</v>
+        <v>96800225</v>
       </c>
       <c r="B14" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554997.4775352756</v>
+        <v>555012</v>
       </c>
       <c r="R14" t="n">
-        <v>6698349.209957663</v>
+        <v>6698370</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2209,22 +2057,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,72 +2087,59 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97330365</v>
+        <v>96801471</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555038.0338900929</v>
+        <v>555013</v>
       </c>
       <c r="R15" t="n">
-        <v>6698219.902395659</v>
+        <v>6698356</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2331,22 +2166,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2361,27 +2196,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97330546</v>
+        <v>96801489</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555011.3967128369</v>
+        <v>555009</v>
       </c>
       <c r="R16" t="n">
-        <v>6698377.578503449</v>
+        <v>6698357</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2445,22 +2275,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2475,27 +2305,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97330541</v>
+        <v>97120236</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2345,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2529,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555016.2686900129</v>
+        <v>555090</v>
       </c>
       <c r="R17" t="n">
-        <v>6698382.592274423</v>
+        <v>6698212</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2559,22 +2393,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2589,63 +2423,68 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97330373</v>
+        <v>97120701</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554999.7546943889</v>
+        <v>555063</v>
       </c>
       <c r="R18" t="n">
-        <v>6698264.276631495</v>
+        <v>6698308</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2672,22 +2511,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,72 +2541,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99589184</v>
+        <v>97120882</v>
       </c>
       <c r="B19" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kyrkberget, Husby, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555017.3542811851</v>
+        <v>555020</v>
       </c>
       <c r="R19" t="n">
-        <v>6698278.37558625</v>
+        <v>6698363</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2794,27 +2629,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fjolårsfru</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,65 +2659,71 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112044200</v>
+        <v>97121049</v>
       </c>
       <c r="B20" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555046</v>
+        <v>555003</v>
       </c>
       <c r="R20" t="n">
-        <v>6698231</v>
+        <v>6698356</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2911,19 +2747,29 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2931,65 +2777,71 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112044198</v>
+        <v>97121063</v>
       </c>
       <c r="B21" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555034</v>
+        <v>555012</v>
       </c>
       <c r="R21" t="n">
-        <v>6698210</v>
+        <v>6698358</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3013,12 +2865,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3033,65 +2895,71 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112044197</v>
+        <v>97121134</v>
       </c>
       <c r="B22" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555034</v>
+        <v>555003</v>
       </c>
       <c r="R22" t="n">
-        <v>6698209</v>
+        <v>6698365</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3115,12 +2983,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,15 +3013,583 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97121317</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555001</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6698364</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>97121323</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>554996</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6698355</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>97330496</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>554994</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6698363</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Intill gammal kolbotten</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97330541</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555016</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6698383</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>97330546</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555011</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6698378</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58719-2021 artfynd.xlsx
+++ b/artfynd/A 58719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330373</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589184</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044198</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044165</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121369</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330695</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589220</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120331</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96800107</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96800225</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96801471</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2314,6 +2389,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96801489</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120236</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2550,6 +2635,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120701</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2668,6 +2758,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120882</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2786,6 +2881,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121049</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2904,6 +3004,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121063</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3022,6 +3127,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121134</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3140,6 +3250,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121317</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3258,6 +3373,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121323</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3372,6 +3492,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330496</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3481,6 +3606,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330541</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3590,8 +3720,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>